--- a/cargaCandidatos/Copia de LISTADO MAESTROS INGLÉS.xlsx
+++ b/cargaCandidatos/Copia de LISTADO MAESTROS INGLÉS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\proyectos\gestPlanes\cargaCandidatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BFFD23-6040-4413-8584-EDC7FB3AD831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94169626-AD7E-4267-A1C5-E1E5FFA143D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5F958561-61FC-4838-B0E6-A2413C2BECD6}"/>
   </bookViews>

--- a/cargaCandidatos/Copia de LISTADO MAESTROS INGLÉS.xlsx
+++ b/cargaCandidatos/Copia de LISTADO MAESTROS INGLÉS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\proyectos\gestPlanes\cargaCandidatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94169626-AD7E-4267-A1C5-E1E5FFA143D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE08550-CD71-4F58-AD25-A47147E35ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5F958561-61FC-4838-B0E6-A2413C2BECD6}"/>
   </bookViews>
@@ -831,9 +831,6 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
       <c r="B3" s="2">
         <v>46051</v>
       </c>
